--- a/master/contacts_master.xlsx
+++ b/master/contacts_master.xlsx
@@ -187,8 +187,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ContactsMaster" displayName="ContactsMaster" ref="A1:N17" headerRowCount="1">
-  <autoFilter ref="A1:N17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ContactsMaster" displayName="ContactsMaster" ref="A1:N29" headerRowCount="1">
+  <autoFilter ref="A1:N29"/>
   <tableColumns count="14">
     <tableColumn id="1" name="email"/>
     <tableColumn id="2" name="vertical"/>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -542,7 +542,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -557,12 +557,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
@@ -1372,14 +1372,14 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>etude.notalex@notaires.fr</t>
+          <t>a.dieu@notaires.fr</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>SELARL NOTALEX</t>
+          <t>Office notarial DIEU Alexandre à SAINT-ÉTIENNE (42000) | 1 allée de l’Electronique</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>0477331135</t>
+          <t>0477019566</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1427,19 +1427,19 @@
       <c r="L15" s="7" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>fraisse.pauline@notaires.fr</t>
+          <t>accueil.42023@notaires.fr</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Office notarial Pauline FRAISSE</t>
+          <t>Office notarial VIAJURIS NOTAIRES, SELARL à SAINT-CHAMOND (42400) | 3 route de Saint-Etienne</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Saint-Chamond</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>0634928826</t>
+          <t>0477222342</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1487,19 +1487,19 @@
       <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24T13:22:22.083690+00:00</t>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>office.balayetassocies@bcda.notaires.fr</t>
+          <t>amelie.duperray@notaires.fr</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Balaÿ Notaires (SCP)</t>
+          <t>Office notarial VIAJURIS NOTAIRES, SELARL à SAINT-ÉTIENNE (42000) | 4 rue Chanoine Ploton</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>0477492280</t>
+          <t>0477574535</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1547,12 +1547,732 @@
       <c r="L17" s="7" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr">
         <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>etude.42004@notaires.fr</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Office notarial SCP Frédéric MALLON et Laura LANCRY, Notaires, Associés à SAINT-ÉTIENNE (42000) | 10 place de l'Hôtel de Ville</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>0477254601</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>etude.fraisse.42120@notaires.fr</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Office notarial FRAISSE, SELARL à SAINT-ÉTIENNE (42000) | 1 boulevard Dalgabio</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>0634928826</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>etude.notalex@notaires.fr</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Office notarial NOTALEX, SELARL à SAINT-ÉTIENNE (42000) | 8 allée de l’informatique</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>0477331135</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
           <t>2026-06-24T13:22:22.083690+00:00</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>etude@gononassocies.notaires.fr</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Office notarial SELARL GONON &amp; Associés à SAINT-ÉTIENNE (42000) | 5 rue Mi Carême</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>0477324653</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>fraisse.pauline@notaires.fr</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Office notarial Pauline FRAISSE</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>0634928826</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>2026-06-24T13:22:22.083690+00:00</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24T13:22:22.083690+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>guibert.associes@notaires.fr</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Office notarial SELARL GUIBERT &amp; Associés, Notaires à SAINT-ÉTIENNE (42100) | 109 rue de la Montat</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>0482771140</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>helene.perrier@42100.notaires.fr</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Office notarial PERRIER Hélène à SAINT-ÉTIENNE (42000) | 17 B rue de la Presse</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>0477393000</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>office.balayetassocies@bcda.notaires.fr</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Office notarial BALAY - COURTET - DURON, SARL à SAINT-ÉTIENNE (42000) | 8 place de l'Hôtel de Ville</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>0477492280</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T13:22:22.083690+00:00</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>office42069.balbigny@notaires.fr</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Office notarial SELARL Office GEYSSANT&amp;VIRICEL, Notaires associés à BALBIGNY (42510) | 120 rue de Saint-Etienne</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Balbigny</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>0477281340</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>on2gf@notaires.fr</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Office notarial SELARL ON2GF à SAINT-ÉTIENNE (42000) | 2 rue du Général Foy</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>0477431520</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>ondf@notaires.fr</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Office notarial ROSTAING-MUSSIO et associée, SELARL à SAINT-ÉTIENNE (42000) | 12 place de l'Hôtel de Ville</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>0477494060</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>scp-denieuil@notaires.fr</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>notaires</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Office notarial SCP Guillaume DENIEUIL Sébastien DENIEUIL David DENIEUIL et Benjamin DENIEUIL NOTAIRES ASSOCIES à SAINT-ÉTIENNE (42000) | 3 place du Peuple</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>0477492860</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:56:52.285739+00:00</t>
         </is>
       </c>
     </row>
